--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23321156</v>
+        <v>4379430</v>
       </c>
       <c r="L2" t="n">
-        <v>13893573</v>
+        <v>2358002</v>
       </c>
       <c r="M2" t="n">
-        <v>3540576</v>
+        <v>546962</v>
       </c>
       <c r="N2" t="n">
-        <v>187668</v>
+        <v>19213</v>
       </c>
       <c r="O2" t="n">
-        <v>2090776</v>
+        <v>342951</v>
       </c>
       <c r="P2" t="n">
-        <v>812805</v>
+        <v>131191</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999726414680481</v>
+        <v>0.9999971389770508</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9207767844200134</v>
+        <v>0.8521031141281128</v>
       </c>
       <c r="S2" t="n">
-        <v>0.829560399055481</v>
+        <v>0.7099571824073792</v>
       </c>
       <c r="T2" t="n">
-        <v>0.791240930557251</v>
+        <v>0.6323808431625366</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5197235345840454</v>
+        <v>0.2448576390743256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8287889957427979</v>
+        <v>0.6859170794487</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8903295397758484</v>
+        <v>0.7934715747833252</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>23321156</v>
+        <v>4379430</v>
       </c>
       <c r="E3" t="n">
-        <v>1968237</v>
+        <v>659091</v>
       </c>
       <c r="F3" t="n">
-        <v>23717</v>
+        <v>11560</v>
       </c>
       <c r="G3" t="n">
-        <v>2885</v>
+        <v>1043</v>
       </c>
       <c r="H3" t="n">
-        <v>1337</v>
+        <v>733</v>
       </c>
       <c r="I3" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>50347231</v>
+        <v>10069602</v>
       </c>
       <c r="K3" t="n">
-        <v>54755489</v>
+        <v>10603992</v>
       </c>
       <c r="L3" t="n">
-        <v>62825913</v>
+        <v>12162572</v>
       </c>
       <c r="M3" t="n">
-        <v>76475295</v>
+        <v>15162919</v>
       </c>
       <c r="N3" t="n">
-        <v>81459996</v>
+        <v>16267328</v>
       </c>
       <c r="O3" t="n">
-        <v>79101236</v>
+        <v>15749256</v>
       </c>
       <c r="P3" t="n">
-        <v>81013294</v>
+        <v>16188460</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9211305379867554</v>
+        <v>0.8668904304504395</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8471925854682922</v>
+        <v>0.7166961431503296</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7580611109733582</v>
+        <v>0.5849123001098633</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4202337861061096</v>
+        <v>0.2148648500442505</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8209255933761597</v>
+        <v>0.6728408336639404</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8409038186073303</v>
+        <v>0.6783647537231445</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1897463</v>
+        <v>720804</v>
       </c>
       <c r="E4" t="n">
-        <v>13893573</v>
+        <v>2358002</v>
       </c>
       <c r="F4" t="n">
-        <v>556261</v>
+        <v>186040</v>
       </c>
       <c r="G4" t="n">
-        <v>16274</v>
+        <v>7395</v>
       </c>
       <c r="H4" t="n">
-        <v>33691</v>
+        <v>16611</v>
       </c>
       <c r="I4" t="n">
-        <v>2280</v>
+        <v>1247</v>
       </c>
       <c r="J4" t="n">
-        <v>869</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>2006541</v>
+        <v>760124</v>
       </c>
       <c r="L4" t="n">
-        <v>2854542</v>
+        <v>963328</v>
       </c>
       <c r="M4" t="n">
-        <v>934137</v>
+        <v>317963</v>
       </c>
       <c r="N4" t="n">
-        <v>173424</v>
+        <v>59253</v>
       </c>
       <c r="O4" t="n">
-        <v>431912</v>
+        <v>157038</v>
       </c>
       <c r="P4" t="n">
-        <v>100121</v>
+        <v>34147</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999863505363464</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R4" t="n">
-        <v>0.920953631401062</v>
+        <v>0.8594331741333008</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8382837772369385</v>
+        <v>0.713310718536377</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7742956876754761</v>
+        <v>0.6077210307121277</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4647134244441986</v>
+        <v>0.2288828641176224</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8248385190963745</v>
+        <v>0.679315984249115</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8649111390113831</v>
+        <v>0.7314171195030212</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>67643</v>
+        <v>25487</v>
       </c>
       <c r="E5" t="n">
-        <v>768100</v>
+        <v>261230</v>
       </c>
       <c r="F5" t="n">
-        <v>3540576</v>
+        <v>546962</v>
       </c>
       <c r="G5" t="n">
-        <v>67278</v>
+        <v>21639</v>
       </c>
       <c r="H5" t="n">
-        <v>213350</v>
+        <v>73337</v>
       </c>
       <c r="I5" t="n">
-        <v>13451</v>
+        <v>6463</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1996814</v>
+        <v>672454</v>
       </c>
       <c r="L5" t="n">
-        <v>2505972</v>
+        <v>932098</v>
       </c>
       <c r="M5" t="n">
-        <v>1129992</v>
+        <v>388156</v>
       </c>
       <c r="N5" t="n">
-        <v>258912</v>
+        <v>70206</v>
       </c>
       <c r="O5" t="n">
-        <v>456076</v>
+        <v>166755</v>
       </c>
       <c r="P5" t="n">
-        <v>153780</v>
+        <v>62202</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.99998939037323</v>
+        <v>0.999998927116394</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9512261748313904</v>
+        <v>0.9127328395843506</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9346916079521179</v>
+        <v>0.8845378756523132</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9748522043228149</v>
+        <v>0.9569859504699707</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9947327375411987</v>
+        <v>0.9921138286590576</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9891814589500427</v>
+        <v>0.9802757501602173</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969066381454468</v>
+        <v>0.9941307902336121</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>40979</v>
+        <v>13494</v>
       </c>
       <c r="E6" t="n">
-        <v>76342</v>
+        <v>19650</v>
       </c>
       <c r="F6" t="n">
-        <v>95068</v>
+        <v>24853</v>
       </c>
       <c r="G6" t="n">
-        <v>187668</v>
+        <v>19213</v>
       </c>
       <c r="H6" t="n">
-        <v>43504</v>
+        <v>11141</v>
       </c>
       <c r="I6" t="n">
-        <v>2951</v>
+        <v>1058</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="E7" t="n">
-        <v>39901</v>
+        <v>22240</v>
       </c>
       <c r="F7" t="n">
-        <v>250857</v>
+        <v>91336</v>
       </c>
       <c r="G7" t="n">
-        <v>83585</v>
+        <v>27521</v>
       </c>
       <c r="H7" t="n">
-        <v>2090776</v>
+        <v>342951</v>
       </c>
       <c r="I7" t="n">
-        <v>81361</v>
+        <v>25352</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>1117</v>
       </c>
       <c r="F8" t="n">
-        <v>8234</v>
+        <v>4174</v>
       </c>
       <c r="G8" t="n">
-        <v>3402</v>
+        <v>1655</v>
       </c>
       <c r="H8" t="n">
-        <v>140030</v>
+        <v>55216</v>
       </c>
       <c r="I8" t="n">
-        <v>812805</v>
+        <v>131191</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
